--- a/CardData/CardEffect.xlsx
+++ b/CardData/CardEffect.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>1792414680082663</author>
+    <author>1792479869308443</author>
   </authors>
   <commentList>
-    <comment ref="D9" authorId="0">
+    <comment ref="D10" authorId="0">
       <text>
         <t>0为攻击表。1为行动表。3为加成表</t>
       </text>
@@ -306,201 +306,222 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>40</v>
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
+    <row r="18">
+      <c r="A18" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
@@ -679,6 +700,7 @@
     <row r="194"/>
     <row r="195"/>
     <row r="196"/>
+    <row r="197"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
